--- a/docs/strategy_log.xlsx
+++ b/docs/strategy_log.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="95">
   <si>
     <t xml:space="preserve">Date Tested</t>
   </si>
@@ -180,6 +180,108 @@
   </si>
   <si>
     <t xml:space="preserve">Same zero-volume issue as VWAP reclaim - re-test on individual NSE stocks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bullish engulfing (candlestick)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liberatedstocktrader.com, tradingrush.net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=0 (best of 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected — not robust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only 33.3% of swept trend_sma combos profitable; trend_sma=50 lost -380.8. The +270.65 top result looks like a lone spike, not a real edge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promising — needs more validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of swept combos profitable, median +1099.65 — the strongest result in this batch. Still single-window in-sample; test on a different date range before considering live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed — not robust enough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=50 lost -1133.43; only 2 of 3 combos profitable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=20, volume_confirm=false (best of 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of swept combos profitable on real volume data — the other standout result. Small absolute P&amp;L (single-share backtest units); needs out-of-sample check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=0, volume_confirm=true (best of 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only 1 of 6 combos profitable; median -6.03. Does not work on SPY.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QQQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=50, volume_confirm=true (best of 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half of swept combos profitable, half not; marginal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VWAP reclaim (re-test, real volume)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-test of 2026-09-02 'untestable on indices' finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (single backtest, not swept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promising — needs sweep + validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real volume data (unlike indices) makes this testable now. Best of the three real-volume stocks; not yet parameter-swept.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed — needs sweep + validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginally positive, close to breakeven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected — negative P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win rate over 50% but avg loss outweighs avg win.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORB + volume confirmation (re-test, real volume)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAPL/SPY/QQQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orb=5/15/30m, volume_mult=1.2/1.5/2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still 0 trades on all 9 combos across all 3 real-volume stocks — this is no longer a zero-volume-data problem, so the volume_mult entry condition itself likely needs review (may be too strict or have a logic issue).</t>
   </si>
   <si>
     <t xml:space="preserve">Strategy Research Summary</t>
@@ -210,12 +312,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -350,8 +453,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,23 +490,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -659,508 +770,940 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3" t="n">
+      <c r="G2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4" t="n">
         <v>195.9</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="3" t="n">
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="4" t="n">
         <v>1686.55</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="3"/>
+      <c r="L3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3" t="n">
+      <c r="G4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="4" t="n">
         <v>456.58</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>0.562</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>593.6</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>0.958</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="G6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>0.516</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <v>3087.9</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4" t="n">
+      <c r="G7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>0.607</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>1823.56</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <v>0.958</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4" t="n">
+      <c r="G8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>0.28</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3" t="n">
+      <c r="I8" s="3"/>
+      <c r="J8" s="4" t="n">
         <v>-164.35</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="6" t="s">
+      <c r="K8" s="3"/>
+      <c r="L8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>0.32</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="3"/>
+      <c r="J9" s="4" t="n">
         <v>-1120</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="6" t="s">
+      <c r="K9" s="3"/>
+      <c r="L9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="G10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>0.36</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="3"/>
+      <c r="J10" s="4" t="n">
         <v>-382.51</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="6" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3" t="n">
+      <c r="G11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="3"/>
+      <c r="L11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3" t="n">
+      <c r="G12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="3"/>
+      <c r="L12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="3" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>270.65</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2495.15</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>293.31</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>-13.88</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1182,115 +1725,115 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="10" t="n">
-        <f aca="false">COUNTA('Strategy Log'!A2:A12)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="10" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!M2:M12,"Yes")</f>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <f aca="false">COUNTA('Strategy Log'!A2:A22)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <f aca="false">COUNTIF('Strategy Log'!M2:M22,"Yes")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!L2:L12,"Rejected")</f>
+      <c r="B5" s="12" t="n">
+        <f aca="false">COUNTIF('Strategy Log'!L2:L22,"Rejected")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!L2:L12,"Untestable on this data")</f>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <f aca="false">COUNTIF('Strategy Log'!L2:L22,"Untestable on this data")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M12,"Yes",'Strategy Log'!H2:H12),"n/a")</f>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M22,"Yes",'Strategy Log'!H2:H22),"n/a")</f>
         <v>0.561666666666667</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M12,"Yes",'Strategy Log'!J2:J12),"n/a")</f>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M22,"Yes",'Strategy Log'!J2:J22),"n/a")</f>
         <v>1835.02</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>59</v>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="A12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/strategy_log.xlsx
+++ b/docs/strategy_log.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="116">
   <si>
     <t xml:space="preserve">Date Tested</t>
   </si>
@@ -282,6 +282,69 @@
   </si>
   <si>
     <t xml:space="preserve">Still 0 trades on all 9 combos across all 3 real-volume stocks — this is no longer a zero-volume-data problem, so the volume_mult entry condition itself likely needs review (may be too strict or have a logic issue).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Param sweep vs 24 combos, extending scope to gold/forex per user request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC=F (Gold futures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orb=15m, sma 20/21 (best of 24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongest result in this batch: 100% of 24 swept combos profitable, median +554.20 - beats several NSE symbols' win rates. Promoted to full 2% ceiling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extending scope to gold/forex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=20 (best of 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robust but weaker than orb_breakout on this symbol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of combos profitable but lower win rate/PnL than orb_breakout on the same symbol - orb_breakout adopted instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USDINR=X (forex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orb=5m, sma 9/20 (best of 24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of swept combos profitable, but tiny absolute PnL (unit-qty backtest on a currency pair quoted ~94) - needs a lot-size-aware re-check before adoption, not just percent robustness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trend_sma=50 (best of 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weaker than orb_breakout on this symbol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robust but lower win rate than orb_breakout on the same pair.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURUSD=X (forex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a - sweep failed (502)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data error — not tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Render returned a 502 mid-sweep (transient cold-start, not a strategy result) - re-run pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (best of 3, all near-zero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected — effectively no edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win rate near 0% on the best combo; total P&amp;L is noise-level. Does not work on this pair.</t>
   </si>
   <si>
     <t xml:space="preserve">Strategy Research Summary</t>
@@ -770,7 +833,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -1274,7 +1337,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>53</v>
       </c>
@@ -1302,7 +1365,7 @@
       <c r="I13" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="4" t="n">
         <v>270.65</v>
       </c>
       <c r="K13" s="5" t="n">
@@ -1318,7 +1381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
         <v>53</v>
       </c>
@@ -1346,7 +1409,7 @@
       <c r="I14" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="4" t="n">
         <v>2495.15</v>
       </c>
       <c r="K14" s="5" t="n">
@@ -1362,7 +1425,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>53</v>
       </c>
@@ -1390,7 +1453,7 @@
       <c r="I15" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="4" t="n">
         <v>293.31</v>
       </c>
       <c r="K15" s="5" t="n">
@@ -1406,7 +1469,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>53</v>
       </c>
@@ -1434,7 +1497,7 @@
       <c r="I16" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="4" t="n">
         <v>56.4</v>
       </c>
       <c r="K16" s="5" t="n">
@@ -1450,7 +1513,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -1478,7 +1541,7 @@
       <c r="I17" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="4" t="n">
         <v>8.07</v>
       </c>
       <c r="K17" s="5" t="n">
@@ -1494,7 +1557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>53</v>
       </c>
@@ -1522,7 +1585,7 @@
       <c r="I18" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="4" t="n">
         <v>32.94</v>
       </c>
       <c r="K18" s="5" t="n">
@@ -1538,7 +1601,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
@@ -1566,7 +1629,7 @@
       <c r="I19" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="4" t="n">
         <v>40.71</v>
       </c>
       <c r="K19" s="3"/>
@@ -1580,7 +1643,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>53</v>
       </c>
@@ -1608,7 +1671,7 @@
       <c r="I20" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="4" t="n">
         <v>11.99</v>
       </c>
       <c r="K20" s="3"/>
@@ -1622,7 +1685,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
@@ -1650,7 +1713,7 @@
       <c r="I21" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="4" t="n">
         <v>-13.88</v>
       </c>
       <c r="K21" s="3"/>
@@ -1664,7 +1727,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
@@ -1690,7 +1753,7 @@
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
@@ -1704,6 +1767,262 @@
       </c>
       <c r="N22" s="3" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>676.5</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>497</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1731,25 +2050,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B3" s="12" t="n">
-        <f aca="false">COUNTA('Strategy Log'!A2:A22)</f>
-        <v>21</v>
+        <f aca="false">COUNTA('Strategy Log'!A2:A28)</f>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B4" s="12" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!M2:M22,"Yes")</f>
-        <v>3</v>
+        <f aca="false">COUNTIF('Strategy Log'!M2:M28,"Yes")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1757,45 +2076,45 @@
         <v>40</v>
       </c>
       <c r="B5" s="12" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!L2:L22,"Rejected")</f>
+        <f aca="false">COUNTIF('Strategy Log'!L2:L28,"Rejected")</f>
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="B6" s="12" t="n">
-        <f aca="false">COUNTIF('Strategy Log'!L2:L22,"Untestable on this data")</f>
+        <f aca="false">COUNTIF('Strategy Log'!L2:L28,"Untestable on this data")</f>
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B7" s="13" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M22,"Yes",'Strategy Log'!H2:H22),"n/a")</f>
-        <v>0.561666666666667</v>
+        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M28,"Yes",'Strategy Log'!H2:H28),"n/a")</f>
+        <v>0.58375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B8" s="14" t="n">
-        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M22,"Yes",'Strategy Log'!J2:J22),"n/a")</f>
-        <v>1835.02</v>
+        <f aca="false">IFERROR(AVERAGEIF('Strategy Log'!M2:M28,"Yes",'Strategy Log'!J2:J28),"n/a")</f>
+        <v>1545.39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
